--- a/exchange_report.xlsx
+++ b/exchange_report.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="관련 뉴스 기사" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="오늘의 환율 현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="데이터 트렌드" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,22 +97,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" indent="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" indent="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -187,6 +191,152 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>최근 7일 환율 추이</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'데이터 트렌드'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'데이터 트렌드'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'데이터 트렌드'!$B$2:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>수집일</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>환율 (KRW)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,9 +631,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +656,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원/달러 환율, 미 고용지표 영향으로 하락 마감</t>
+          <t>금일 환율 하락세, 해외 직구족 늘어날까</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -516,7 +666,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026.05.07</t>
+          <t>2026.05.07 10:00</t>
         </is>
       </c>
     </row>
@@ -531,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -540,6 +690,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,6 +725,16 @@
           <t>등락 여부</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro ($999)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AirPods Pro ($249)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -599,6 +761,16 @@
           <t>하락</t>
         </is>
       </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>1,339,159원</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>333,784원</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -624,6 +796,149 @@
         <is>
           <t>상승</t>
         </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>889,110원</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>221,610원</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1455</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>보합</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>1,453,545원</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>362,295원</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>05.01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>05.02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>05.03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>05.04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05.05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05.06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05.07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1340</v>
       </c>
     </row>
   </sheetData>

--- a/exchange_report.xlsx
+++ b/exchange_report.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="관련 뉴스 기사" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="오늘의 환율 현황" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="데이터 트렌드" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00FCE8E6"/>
+        <bgColor rgb="00FCE8E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE8E6"/>
-        <bgColor rgb="00FCE8E6"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -112,9 +111,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -191,152 +187,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>최근 7일 환율 추이</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'데이터 트렌드'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'데이터 트렌드'!$A$2:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'데이터 트렌드'!$B$2:$B$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>수집일</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>환율 (KRW)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,17 +506,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>금일 환율 하락세, 해외 직구족 늘어날까</t>
+          <t>환율, 외국인 순매도에 낙폭 축소…1.1원 내린 1,454.0원</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>https://kita.net/news/123</t>
+          <t>https://kita.net/cmmrcInfo/ehgtNews/ehgtNewsDetail.do?classification=6&amp;no=101367</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026.05.07 10:00</t>
+          <t>2026.05.07</t>
         </is>
       </c>
     </row>
@@ -743,202 +593,105 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1340.5</v>
+        <v>1480.5</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1350</v>
+        <v>1456.8</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-9.5</v>
+        <v>23.7</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>하락</t>
+          <t>상승</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1,339,159원</t>
+          <t>1,479,019원</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>333,784원</t>
+          <t>368,644원</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>JPY(100)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>885.5</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>980</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>931.8200000000001</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>5.17%</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>상승</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>889,110원</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>221,610원</t>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>979,020원</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>244,020원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1455</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1455</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>보합</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>1,453,545원</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>362,295원</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>05.01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>05.02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>05.03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>05.04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>05.05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>05.06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>05.07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1340</v>
+      <c r="B4" s="5" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1712.03</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-132.03</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>-7.71%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>하락</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1,578,420원</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>393,420원</t>
+        </is>
       </c>
     </row>
   </sheetData>
